--- a/data/trans_orig/P05A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>149806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194231</t>
+          <t>192210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126772</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164004</t>
+          <t>164078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>285061</t>
+          <t>288306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345384</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198254</t>
+          <t>199509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243243</t>
+          <t>241700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>204104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243597</t>
+          <t>243811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>416029</t>
+          <t>414470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>474972</t>
+          <t>473480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82431</t>
+          <t>81878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117013</t>
+          <t>118612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82314</t>
+          <t>81539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115627</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>174485</t>
+          <t>170210</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>220928</t>
+          <t>220426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229803</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281761</t>
+          <t>283786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153558</t>
+          <t>151699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199186</t>
+          <t>196700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397391</t>
+          <t>396657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467527</t>
+          <t>470250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>327540</t>
+          <t>325594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>382816</t>
+          <t>379725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>305882</t>
+          <t>301222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353124</t>
+          <t>353322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>639987</t>
+          <t>645182</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>714887</t>
+          <t>719150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>145530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100089</t>
+          <t>99365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139572</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215995</t>
+          <t>213362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272689</t>
+          <t>271772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168286</t>
+          <t>168374</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>216149</t>
+          <t>216075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213245</t>
+          <t>213850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265618</t>
+          <t>265398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>391096</t>
+          <t>394441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>464705</t>
+          <t>463204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>293672</t>
+          <t>293437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345621</t>
+          <t>345907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289711</t>
+          <t>292557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>345429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598361</t>
+          <t>599996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>675956</t>
+          <t>670804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105263</t>
+          <t>107615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148692</t>
+          <t>150354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115720</t>
+          <t>115633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156288</t>
+          <t>157191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233714</t>
+          <t>235717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297710</t>
+          <t>294614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151080</t>
+          <t>151363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194520</t>
+          <t>194719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120824</t>
+          <t>121890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161044</t>
+          <t>161559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>287111</t>
+          <t>284441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343725</t>
+          <t>342382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217778</t>
+          <t>219132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263850</t>
+          <t>265927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>247831</t>
+          <t>249984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292999</t>
+          <t>293560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>481094</t>
+          <t>482195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544009</t>
+          <t>545313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85321</t>
+          <t>85052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>122041</t>
+          <t>123095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>83803</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120682</t>
+          <t>119521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180102</t>
+          <t>180360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>233336</t>
+          <t>231360</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106184</t>
+          <t>107004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141779</t>
+          <t>142222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>151638</t>
+          <t>154518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232661</t>
+          <t>231060</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>280948</t>
+          <t>284055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>177699</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>215615</t>
+          <t>216692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177370</t>
+          <t>176012</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>217546</t>
+          <t>214901</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>366628</t>
+          <t>367800</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>423947</t>
+          <t>422171</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48759</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>77693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>58391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89521</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115003</t>
+          <t>116116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158593</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74510</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105171</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95565</t>
+          <t>95032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127248</t>
+          <t>128373</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>179127</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>223930</t>
+          <t>224768</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144112</t>
+          <t>144183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176556</t>
+          <t>176472</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151442</t>
+          <t>151215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187255</t>
+          <t>187069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>307425</t>
+          <t>305617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>354167</t>
+          <t>354269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>54979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75680</t>
+          <t>75220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84099</t>
+          <t>86374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120093</t>
+          <t>121599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>53713</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>79607</t>
+          <t>80476</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90291</t>
+          <t>90559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126126</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>151742</t>
+          <t>152505</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>196198</t>
+          <t>197096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93130</t>
+          <t>93572</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121359</t>
+          <t>123627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148841</t>
+          <t>147156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>185388</t>
+          <t>186505</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>249884</t>
+          <t>253331</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299184</t>
+          <t>298530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46398</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44928</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73980</t>
+          <t>76237</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76937</t>
+          <t>78107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>115683</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1022118</t>
+          <t>1020819</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1128639</t>
+          <t>1132825</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>995094</t>
+          <t>993982</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1106850</t>
+          <t>1104160</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2045308</t>
+          <t>2048112</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2201402</t>
+          <t>2193004</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1537180</t>
+          <t>1540307</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1660123</t>
+          <t>1657325</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1618564</t>
+          <t>1614570</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1729902</t>
+          <t>1729953</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3192424</t>
+          <t>3184798</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3363682</t>
+          <t>3357488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>550722</t>
+          <t>549875</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>639030</t>
+          <t>641177</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>598882</t>
+          <t>603895</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>694705</t>
+          <t>690548</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1178313</t>
+          <t>1174107</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1300924</t>
+          <t>1310400</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134022</t>
+          <t>133905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175445</t>
+          <t>174367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131694</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170262</t>
+          <t>169850</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>278543</t>
+          <t>277472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332640</t>
+          <t>332352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175152</t>
+          <t>177486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218298</t>
+          <t>220214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156394</t>
+          <t>154805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>194616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342918</t>
+          <t>341964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>400559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>86618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122451</t>
+          <t>122596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119644</t>
+          <t>120556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>183635</t>
+          <t>182593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229918</t>
+          <t>232851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216124</t>
+          <t>213780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267074</t>
+          <t>265649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197792</t>
+          <t>197265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247119</t>
+          <t>246357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428314</t>
+          <t>425283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495266</t>
+          <t>497998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241517</t>
+          <t>240248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293610</t>
+          <t>294771</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>240229</t>
+          <t>238759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>288721</t>
+          <t>289322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>502013</t>
+          <t>498869</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>570819</t>
+          <t>568033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151221</t>
+          <t>148778</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199707</t>
+          <t>198401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105035</t>
+          <t>104277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145036</t>
+          <t>145742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268294</t>
+          <t>268570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>327089</t>
+          <t>328723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186975</t>
+          <t>188780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238827</t>
+          <t>237476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>217399</t>
+          <t>216739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>268861</t>
+          <t>270177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>417787</t>
+          <t>418526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>489597</t>
+          <t>490147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275154</t>
+          <t>277659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>328621</t>
+          <t>331451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260869</t>
+          <t>262553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313868</t>
+          <t>315345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550965</t>
+          <t>552393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>626713</t>
+          <t>628511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144572</t>
+          <t>143085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188898</t>
+          <t>189820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153038</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200350</t>
+          <t>201177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309893</t>
+          <t>313465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376427</t>
+          <t>379106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166330</t>
+          <t>168220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215759</t>
+          <t>217437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181132</t>
+          <t>180278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230365</t>
+          <t>230973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,47 +6034,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>37,75%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>397346</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>362703</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>432361</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>32,42%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>397346</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>362933</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>432177</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242970</t>
+          <t>243198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294899</t>
+          <t>293893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212175</t>
+          <t>209311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263039</t>
+          <t>262628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467214</t>
+          <t>469311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540196</t>
+          <t>541626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133140</t>
+          <t>129680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176705</t>
+          <t>175453</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148469</t>
+          <t>148351</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>195105</t>
+          <t>193921</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>292624</t>
+          <t>294349</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>358761</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150597</t>
+          <t>149459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,47 +6455,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>25,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>137145</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>116061</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>156833</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>26,22%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>137145</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>118505</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>156511</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>30,99%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239141</t>
+          <t>238403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>297123</t>
+          <t>294606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156169</t>
+          <t>157517</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>199156</t>
+          <t>199281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>178828</t>
+          <t>176455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>221996</t>
+          <t>220632</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>348640</t>
+          <t>348821</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>410002</t>
+          <t>409794</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101173</t>
+          <t>100997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138718</t>
+          <t>137299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>125511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200585</t>
+          <t>198205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252305</t>
+          <t>250331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116400</t>
+          <t>117879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>76837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>108150</t>
+          <t>109638</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>169740</t>
+          <t>168627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>215665</t>
+          <t>217779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109570</t>
+          <t>111657</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148521</t>
+          <t>148056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148348</t>
+          <t>148131</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>185728</t>
+          <t>185310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>271862</t>
+          <t>270371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324487</t>
+          <t>324774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64933</t>
+          <t>65585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96281</t>
+          <t>97239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76132</t>
+          <t>76307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>107057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149788</t>
+          <t>147386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>191984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59004</t>
+          <t>57772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88259</t>
+          <t>88124</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98128</t>
+          <t>100227</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137275</t>
+          <t>138270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169819</t>
+          <t>169390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215402</t>
+          <t>217974</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>93832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>125629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165862</t>
+          <t>164870</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>206500</t>
+          <t>204459</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>267781</t>
+          <t>268534</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>319995</t>
+          <t>320556</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47109</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>74016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99981</t>
+          <t>101512</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125370</t>
+          <t>121616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>169885</t>
+          <t>165874</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1044329</t>
+          <t>1045744</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1160263</t>
+          <t>1161026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1111024</t>
+          <t>1115924</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1230356</t>
+          <t>1226746</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2181424</t>
+          <t>2186277</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2353032</t>
+          <t>2346598</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1388495</t>
+          <t>1385916</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1510917</t>
+          <t>1512008</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1454052</t>
+          <t>1458119</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1578408</t>
+          <t>1569442</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2883046</t>
+          <t>2889649</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3060613</t>
+          <t>3064122</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>808419</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>915311</t>
+          <t>907549</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>806088</t>
+          <t>806960</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>907061</t>
+          <t>913131</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1643546</t>
+          <t>1637211</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1793226</t>
+          <t>1782199</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137616</t>
+          <t>139087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177298</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145739</t>
+          <t>145251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183844</t>
+          <t>185811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292686</t>
+          <t>290180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>347309</t>
+          <t>346057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143442</t>
+          <t>142981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181964</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133068</t>
+          <t>132909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169814</t>
+          <t>171925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287033</t>
+          <t>285919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341438</t>
+          <t>342377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>81566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115884</t>
+          <t>117821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>63070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>93668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154792</t>
+          <t>152558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200454</t>
+          <t>201920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195497</t>
+          <t>196640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243986</t>
+          <t>245228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193997</t>
+          <t>193987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237234</t>
+          <t>235962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402475</t>
+          <t>402848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469268</t>
+          <t>470067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>222741</t>
+          <t>222442</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>271144</t>
+          <t>270758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203507</t>
+          <t>205496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>249437</t>
+          <t>250320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>438748</t>
+          <t>438117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>506807</t>
+          <t>505001</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104336</t>
+          <t>104606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143364</t>
+          <t>143645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103022</t>
+          <t>101262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141160</t>
+          <t>139783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218555</t>
+          <t>217772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>271104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>226918</t>
+          <t>229702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279111</t>
+          <t>278831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221623</t>
+          <t>223909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271484</t>
+          <t>271671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>464543</t>
+          <t>463160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>536475</t>
+          <t>537821</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>238512</t>
+          <t>240158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292924</t>
+          <t>289789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228769</t>
+          <t>227756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275484</t>
+          <t>274016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482291</t>
+          <t>481295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>556831</t>
+          <t>553912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125286</t>
+          <t>126618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>168929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142183</t>
+          <t>141981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185546</t>
+          <t>186083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280033</t>
+          <t>281450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343453</t>
+          <t>344279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>201068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>249606</t>
+          <t>251202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239186</t>
+          <t>239364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289445</t>
+          <t>288868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454602</t>
+          <t>452906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>525041</t>
+          <t>524325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219169</t>
+          <t>216469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269987</t>
+          <t>267680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204194</t>
+          <t>206620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254322</t>
+          <t>254414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>437686</t>
+          <t>441378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505516</t>
+          <t>512006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>153017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200007</t>
+          <t>198987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134575</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179380</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298025</t>
+          <t>297338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>365047</t>
+          <t>360390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202250</t>
+          <t>203213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>169759</t>
+          <t>168701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214582</t>
+          <t>215273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>339515</t>
+          <t>338381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402129</t>
+          <t>400358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170068</t>
+          <t>171431</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>213747</t>
+          <t>215540</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180756</t>
+          <t>184209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>227697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>366405</t>
+          <t>364313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>429645</t>
+          <t>430061</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87843</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125783</t>
+          <t>123590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81085</t>
+          <t>83096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>122088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181913</t>
+          <t>180578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>233661</t>
+          <t>235777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115392</t>
+          <t>116154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150435</t>
+          <t>150993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>134247</t>
+          <t>136507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173670</t>
+          <t>174947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>263902</t>
+          <t>261913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>313496</t>
+          <t>311802</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98436</t>
+          <t>97507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>133928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121313</t>
+          <t>118916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>158309</t>
+          <t>156856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>230246</t>
+          <t>229719</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>280541</t>
+          <t>282347</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>68997</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101152</t>
+          <t>101102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>65185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98605</t>
+          <t>98606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143088</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188222</t>
+          <t>186692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83969</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112375</t>
+          <t>112973</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>154670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>197609</t>
+          <t>200901</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>251230</t>
+          <t>243567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>301364</t>
+          <t>300112</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>95324</t>
+          <t>94596</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123998</t>
+          <t>123093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130880</t>
+          <t>128652</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175219</t>
+          <t>171866</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234424</t>
+          <t>233580</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286680</t>
+          <t>287698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37410</t>
+          <t>37482</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60280</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88581</t>
+          <t>87825</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99459</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>138832</t>
+          <t>140078</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1200614</t>
+          <t>1205618</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1320159</t>
+          <t>1320986</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1345036</t>
+          <t>1349350</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1467578</t>
+          <t>1466807</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2594422</t>
+          <t>2584107</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2757183</t>
+          <t>2752705</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1275693</t>
+          <t>1284468</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1396378</t>
+          <t>1397976</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1296826</t>
+          <t>1293371</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1415686</t>
+          <t>1409948</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2595275</t>
+          <t>2605102</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2766095</t>
+          <t>2770010</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>732286</t>
+          <t>730207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>831179</t>
+          <t>830573</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>719000</t>
+          <t>719031</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>818859</t>
+          <t>817253</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1480348</t>
+          <t>1473339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1618375</t>
+          <t>1621826</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>45281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>37173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58543</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63760</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57276</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106924</t>
+          <t>105049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311061</t>
+          <t>310359</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>358729</t>
+          <t>358888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>218622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>259735</t>
+          <t>258915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>543730</t>
+          <t>545062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>607388</t>
+          <t>608917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21303</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53582</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62555</t>
+          <t>61800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57570</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100052</t>
+          <t>103422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40084</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77704</t>
+          <t>79364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>268168</t>
+          <t>282795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>105860</t>
+          <t>108350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>354954</t>
+          <t>364072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>306419</t>
+          <t>306057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>353055</t>
+          <t>352721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>215074</t>
+          <t>200031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>409413</t>
+          <t>409814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>510072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>747375</t>
+          <t>744142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>44893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>74457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>35800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>62613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>86579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129356</t>
+          <t>127889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54001</t>
+          <t>55050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86804</t>
+          <t>88884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>62402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104696</t>
+          <t>104177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182162</t>
+          <t>182262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>385366</t>
+          <t>384982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>426513</t>
+          <t>427032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431700</t>
+          <t>433196</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487333</t>
+          <t>490205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>828469</t>
+          <t>828318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>900070</t>
+          <t>903180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24141</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>88070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59509</t>
+          <t>58590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86991</t>
+          <t>87231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74792</t>
+          <t>74544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164818</t>
+          <t>164258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149480</t>
+          <t>151475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70235</t>
+          <t>68792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100416</t>
+          <t>99513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>109802</t>
+          <t>114946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230700</t>
+          <t>233830</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>659777</t>
+          <t>656192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>813150</t>
+          <t>821748</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534134</t>
+          <t>534870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>577275</t>
+          <t>579872</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1210768</t>
+          <t>1209805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1423117</t>
+          <t>1420631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57453</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41009</t>
+          <t>40723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61040</t>
+          <t>60806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80567</t>
+          <t>79271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110316</t>
+          <t>110873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54917</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83986</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>67555</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92989</t>
+          <t>93385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128298</t>
+          <t>128481</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166890</t>
+          <t>167198</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>430601</t>
+          <t>430546</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>466006</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>400458</t>
+          <t>401829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>431829</t>
+          <t>432429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>844087</t>
+          <t>842519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>892581</t>
+          <t>889466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>47800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>454291</t>
+          <t>451973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77347</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>645945</t>
+          <t>630830</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57948</t>
+          <t>58402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94132</t>
+          <t>93917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53119</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140693</t>
+          <t>140599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277228</t>
+          <t>277241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>302294</t>
+          <t>302618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128658</t>
+          <t>129713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>471354</t>
+          <t>472281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279142</t>
+          <t>289678</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>764647</t>
+          <t>764707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75468</t>
+          <t>75698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>91235</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>120463</t>
+          <t>121712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>215087</t>
+          <t>213754</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>236838</t>
+          <t>234698</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>321226</t>
+          <t>320118</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>346163</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>543003</t>
+          <t>542241</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>575495</t>
+          <t>576378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>212815</t>
+          <t>207074</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>306624</t>
+          <t>310529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>317340</t>
+          <t>313415</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1101682</t>
+          <t>1111643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>570529</t>
+          <t>568924</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1474286</t>
+          <t>1466265</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>319702</t>
+          <t>335004</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>469221</t>
+          <t>473837</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>448277</t>
+          <t>446845</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>735213</t>
+          <t>728721</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>826305</t>
+          <t>843507</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1164285</t>
+          <t>1158282</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2703469</t>
+          <t>2695481</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2941023</t>
+          <t>2912984</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2164050</t>
+          <t>2165341</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2853912</t>
+          <t>2848636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4873202</t>
+          <t>4899739</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5654232</t>
+          <t>5653815</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">

--- a/data/trans_orig/P05A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>149736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192210</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126895</t>
+          <t>126275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164078</t>
+          <t>164114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>285722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>343531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199509</t>
+          <t>199350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241700</t>
+          <t>242901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204104</t>
+          <t>203385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243811</t>
+          <t>243988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414470</t>
+          <t>414614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473480</t>
+          <t>474215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81878</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118612</t>
+          <t>115774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81539</t>
+          <t>82217</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115607</t>
+          <t>115532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170210</t>
+          <t>174956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>220426</t>
+          <t>222572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>232414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283786</t>
+          <t>285660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151699</t>
+          <t>152733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196700</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396657</t>
+          <t>398730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>470250</t>
+          <t>469491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>325594</t>
+          <t>324094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>379725</t>
+          <t>378945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>301222</t>
+          <t>305049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353322</t>
+          <t>353816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>644172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>719150</t>
+          <t>716213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103983</t>
+          <t>103743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145530</t>
+          <t>144968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>99500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142032</t>
+          <t>141920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213362</t>
+          <t>215329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271772</t>
+          <t>274610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168374</t>
+          <t>169654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>216075</t>
+          <t>216120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>213850</t>
+          <t>212563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265398</t>
+          <t>265298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394441</t>
+          <t>397328</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>463204</t>
+          <t>462503</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>293437</t>
+          <t>293949</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345907</t>
+          <t>343282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292557</t>
+          <t>289441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345429</t>
+          <t>341528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>599996</t>
+          <t>598954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>670804</t>
+          <t>670850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107615</t>
+          <t>108441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150354</t>
+          <t>149751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115633</t>
+          <t>115390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157191</t>
+          <t>158206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235717</t>
+          <t>234906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294614</t>
+          <t>292498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151363</t>
+          <t>151585</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194719</t>
+          <t>195519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121890</t>
+          <t>121227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161559</t>
+          <t>162749</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284441</t>
+          <t>280310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342382</t>
+          <t>345051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219132</t>
+          <t>217888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265927</t>
+          <t>264679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249984</t>
+          <t>248781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>293560</t>
+          <t>296418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482195</t>
+          <t>481115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>545313</t>
+          <t>546931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85052</t>
+          <t>85598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123095</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83803</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119521</t>
+          <t>121721</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180360</t>
+          <t>180251</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>231607</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107004</t>
+          <t>106946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142222</t>
+          <t>142282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>114238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154518</t>
+          <t>152016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231060</t>
+          <t>232899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284055</t>
+          <t>286007</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>178514</t>
+          <t>177751</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>216692</t>
+          <t>216992</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176012</t>
+          <t>177794</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>214901</t>
+          <t>218524</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>367800</t>
+          <t>365792</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>422171</t>
+          <t>420223</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>49185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77693</t>
+          <t>78403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58391</t>
+          <t>58295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116116</t>
+          <t>114465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158290</t>
+          <t>155381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75314</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105686</t>
+          <t>106236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95032</t>
+          <t>96149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128373</t>
+          <t>128284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>178124</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>224768</t>
+          <t>223491</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144183</t>
+          <t>144812</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176472</t>
+          <t>176577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151215</t>
+          <t>152224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187069</t>
+          <t>186487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>305617</t>
+          <t>307341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>354269</t>
+          <t>355875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>31539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>55032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>75354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86374</t>
+          <t>86164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121599</t>
+          <t>121423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80476</t>
+          <t>80219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90559</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126556</t>
+          <t>125826</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152505</t>
+          <t>153911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>197096</t>
+          <t>196808</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93572</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123627</t>
+          <t>120960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147156</t>
+          <t>147896</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>186505</t>
+          <t>188861</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>253331</t>
+          <t>248175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>298530</t>
+          <t>296559</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>46701</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>76237</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>77552</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>115683</t>
+          <t>116359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1020819</t>
+          <t>1019364</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1132825</t>
+          <t>1121126</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>998673</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1104160</t>
+          <t>1107392</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2048112</t>
+          <t>2046207</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2193004</t>
+          <t>2196875</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1540307</t>
+          <t>1543587</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1657325</t>
+          <t>1657056</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1614570</t>
+          <t>1615658</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1729953</t>
+          <t>1728967</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3184798</t>
+          <t>3192964</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3357488</t>
+          <t>3351784</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>549875</t>
+          <t>554313</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>641177</t>
+          <t>639575</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>603895</t>
+          <t>604021</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>690548</t>
+          <t>691230</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1174107</t>
+          <t>1181043</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1310400</t>
+          <t>1301389</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133905</t>
+          <t>133571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174367</t>
+          <t>174648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131865</t>
+          <t>131035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169850</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>277472</t>
+          <t>276245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332352</t>
+          <t>332236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>172896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220214</t>
+          <t>216773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154805</t>
+          <t>155092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194616</t>
+          <t>197038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>341964</t>
+          <t>343493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>400559</t>
+          <t>401564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122596</t>
+          <t>121431</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84320</t>
+          <t>86130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120556</t>
+          <t>120114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>182593</t>
+          <t>183111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232851</t>
+          <t>232689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213780</t>
+          <t>213975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265649</t>
+          <t>266970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197265</t>
+          <t>196597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246357</t>
+          <t>244638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425283</t>
+          <t>427418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497998</t>
+          <t>498173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>240248</t>
+          <t>245214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>294771</t>
+          <t>294149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>238759</t>
+          <t>241456</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289322</t>
+          <t>291377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>498869</t>
+          <t>497720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>568033</t>
+          <t>570732</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148778</t>
+          <t>149463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198401</t>
+          <t>197747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104277</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145742</t>
+          <t>145419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>265248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328723</t>
+          <t>327556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188780</t>
+          <t>187566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>239931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216739</t>
+          <t>214115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>270177</t>
+          <t>267387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>418526</t>
+          <t>422065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>490147</t>
+          <t>487804</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>277659</t>
+          <t>275725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>331451</t>
+          <t>330102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>262553</t>
+          <t>262006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>315345</t>
+          <t>316691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552393</t>
+          <t>556971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628511</t>
+          <t>634306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143085</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189820</t>
+          <t>191627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155208</t>
+          <t>153188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201177</t>
+          <t>200368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313465</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379106</t>
+          <t>378761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168220</t>
+          <t>167924</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217437</t>
+          <t>217688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180278</t>
+          <t>183339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230973</t>
+          <t>230632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362703</t>
+          <t>365703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432361</t>
+          <t>438827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243198</t>
+          <t>241688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293893</t>
+          <t>294074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209311</t>
+          <t>211036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>262628</t>
+          <t>260410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>469311</t>
+          <t>466592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>541626</t>
+          <t>543615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129680</t>
+          <t>131921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175453</t>
+          <t>176242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>148428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193921</t>
+          <t>195299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>294349</t>
+          <t>291610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358761</t>
+          <t>355289</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110937</t>
+          <t>110346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149459</t>
+          <t>151092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116061</t>
+          <t>118600</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156833</t>
+          <t>155529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238403</t>
+          <t>240134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>294606</t>
+          <t>296673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>157517</t>
+          <t>158062</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>199281</t>
+          <t>201211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176455</t>
+          <t>178311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>220632</t>
+          <t>220759</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>345480</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>409794</t>
+          <t>406527</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100997</t>
+          <t>99373</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137299</t>
+          <t>138834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88445</t>
+          <t>89155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125511</t>
+          <t>125952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198205</t>
+          <t>199322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>250331</t>
+          <t>252942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82093</t>
+          <t>81052</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117879</t>
+          <t>116526</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76837</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109638</t>
+          <t>111676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>168627</t>
+          <t>171096</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>217779</t>
+          <t>218950</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>112258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148056</t>
+          <t>149138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148131</t>
+          <t>148115</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>185310</t>
+          <t>185373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>270371</t>
+          <t>269331</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324774</t>
+          <t>322348</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65585</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76307</t>
+          <t>75306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107057</t>
+          <t>108306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147386</t>
+          <t>148055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>191984</t>
+          <t>194406</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57772</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88124</t>
+          <t>89360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100296</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138270</t>
+          <t>137080</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169390</t>
+          <t>167003</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>217974</t>
+          <t>216477</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93832</t>
+          <t>92476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125629</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>164870</t>
+          <t>165571</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>204459</t>
+          <t>205809</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>268534</t>
+          <t>265777</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>320556</t>
+          <t>320601</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47030</t>
+          <t>47957</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74016</t>
+          <t>76567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67493</t>
+          <t>68467</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101512</t>
+          <t>100695</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>121616</t>
+          <t>122968</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>165874</t>
+          <t>165724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1045744</t>
+          <t>1047007</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1161026</t>
+          <t>1165883</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1115924</t>
+          <t>1109950</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1226746</t>
+          <t>1223368</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2186277</t>
+          <t>2189060</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2346598</t>
+          <t>2349861</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1385916</t>
+          <t>1398320</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1512008</t>
+          <t>1519295</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1458119</t>
+          <t>1456621</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1569442</t>
+          <t>1578633</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2889649</t>
+          <t>2883667</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3064122</t>
+          <t>3049725</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>798675</t>
+          <t>800392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>907549</t>
+          <t>902620</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>806960</t>
+          <t>802387</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>913131</t>
+          <t>909200</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1637211</t>
+          <t>1634358</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1782199</t>
+          <t>1785675</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139087</t>
+          <t>137932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180272</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145251</t>
+          <t>145441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185811</t>
+          <t>182593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>290180</t>
+          <t>292514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346057</t>
+          <t>348696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142981</t>
+          <t>143112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>182595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132909</t>
+          <t>132885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171925</t>
+          <t>169624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285919</t>
+          <t>288730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>342377</t>
+          <t>342726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>81799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117821</t>
+          <t>115777</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>62771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93668</t>
+          <t>94215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152558</t>
+          <t>155391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201920</t>
+          <t>201290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196640</t>
+          <t>198776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245228</t>
+          <t>245806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193987</t>
+          <t>190808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235962</t>
+          <t>236952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402848</t>
+          <t>400822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>470067</t>
+          <t>465326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>222442</t>
+          <t>221912</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>270758</t>
+          <t>269719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205496</t>
+          <t>205110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>250320</t>
+          <t>249429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>438117</t>
+          <t>439842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>505001</t>
+          <t>505193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104606</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143645</t>
+          <t>143225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101262</t>
+          <t>101810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139783</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217772</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271104</t>
+          <t>273847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229702</t>
+          <t>229219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>278831</t>
+          <t>278829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>223909</t>
+          <t>221945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271671</t>
+          <t>269838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>463160</t>
+          <t>467510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>537821</t>
+          <t>536095</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240158</t>
+          <t>239212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289789</t>
+          <t>290470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227756</t>
+          <t>226333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274016</t>
+          <t>277432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481295</t>
+          <t>481083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>553912</t>
+          <t>551944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126618</t>
+          <t>126428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168929</t>
+          <t>169447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141981</t>
+          <t>143526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186083</t>
+          <t>187800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281450</t>
+          <t>282070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344279</t>
+          <t>346210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201068</t>
+          <t>196823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>251202</t>
+          <t>247279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239364</t>
+          <t>241006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288868</t>
+          <t>291302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>452906</t>
+          <t>455347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>524325</t>
+          <t>525811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>216469</t>
+          <t>218061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267680</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206620</t>
+          <t>206170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254414</t>
+          <t>254473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>441378</t>
+          <t>438158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>512006</t>
+          <t>510037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153017</t>
+          <t>149678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198987</t>
+          <t>197652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133840</t>
+          <t>134174</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>178359</t>
+          <t>178570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297338</t>
+          <t>297241</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>360390</t>
+          <t>361698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158218</t>
+          <t>158035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203213</t>
+          <t>203835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168701</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215273</t>
+          <t>212521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338381</t>
+          <t>339223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>400358</t>
+          <t>403919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>168912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>215540</t>
+          <t>213567</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184209</t>
+          <t>181648</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>227697</t>
+          <t>228165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>364313</t>
+          <t>364337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>430061</t>
+          <t>429095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>86590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123590</t>
+          <t>123074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83096</t>
+          <t>81755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122088</t>
+          <t>119858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180578</t>
+          <t>180509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>235777</t>
+          <t>231447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116154</t>
+          <t>114602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>150993</t>
+          <t>149918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136507</t>
+          <t>135973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174947</t>
+          <t>174600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>261913</t>
+          <t>262183</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>311802</t>
+          <t>312698</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97507</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133928</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118916</t>
+          <t>120143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156856</t>
+          <t>156851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>229719</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282347</t>
+          <t>281487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101102</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65185</t>
+          <t>64535</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98606</t>
+          <t>97091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142165</t>
+          <t>141852</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186692</t>
+          <t>187015</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85888</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112973</t>
+          <t>113073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154670</t>
+          <t>154121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>200901</t>
+          <t>201467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>243567</t>
+          <t>247563</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300112</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94596</t>
+          <t>94704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123093</t>
+          <t>123168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128652</t>
+          <t>128808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171866</t>
+          <t>174183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233580</t>
+          <t>232827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>287698</t>
+          <t>287672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60876</t>
+          <t>61508</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>52270</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87825</t>
+          <t>87279</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>98208</t>
+          <t>96752</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140078</t>
+          <t>139204</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1205618</t>
+          <t>1207646</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1320986</t>
+          <t>1327275</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1349350</t>
+          <t>1347223</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1466807</t>
+          <t>1471061</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2584107</t>
+          <t>2596230</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2752705</t>
+          <t>2754297</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1284468</t>
+          <t>1274584</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1397976</t>
+          <t>1392536</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1293371</t>
+          <t>1298858</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1409948</t>
+          <t>1412734</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2605102</t>
+          <t>2607243</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2770010</t>
+          <t>2765495</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>730207</t>
+          <t>731615</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>830573</t>
+          <t>835657</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>719031</t>
+          <t>719651</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>817253</t>
+          <t>821941</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1473339</t>
+          <t>1478430</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1621826</t>
+          <t>1618976</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>50725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54655</t>
+          <t>60492</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>41895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80863</t>
+          <t>86322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34682</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,27 +12525,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43426</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>73319</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>78109</t>
+          <t>87553</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105049</t>
+          <t>117305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>339207</t>
+          <t>341121</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310359</t>
+          <t>313180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>358888</t>
+          <t>361228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>241216</t>
+          <t>281138</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>218622</t>
+          <t>257459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258915</t>
+          <t>299565</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>580423</t>
+          <t>622259</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>545062</t>
+          <t>587563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>608917</t>
+          <t>649436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>48637</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>64256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>83375</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>64479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103422</t>
+          <t>107027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57586</t>
+          <t>63867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>45180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79364</t>
+          <t>87923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117846</t>
+          <t>63161</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>282795</t>
+          <t>80844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>175432</t>
+          <t>127029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108350</t>
+          <t>102496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>364072</t>
+          <t>155749</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>332108</t>
+          <t>378285</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>306057</t>
+          <t>350606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352721</t>
+          <t>399647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>348984</t>
+          <t>388959</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200031</t>
+          <t>367086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>409814</t>
+          <t>407341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>681093</t>
+          <t>767244</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>510072</t>
+          <t>736040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>744142</t>
+          <t>797222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57672</t>
+          <t>64992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74457</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48793</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62613</t>
+          <t>69068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>106465</t>
+          <t>120397</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86579</t>
+          <t>102679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127889</t>
+          <t>141920</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>83105</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55050</t>
+          <t>66055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88884</t>
+          <t>100928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86871</t>
+          <t>100362</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62402</t>
+          <t>86072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104177</t>
+          <t>117733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>183467</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128964</t>
+          <t>160514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182262</t>
+          <t>211826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407013</t>
+          <t>469358</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>384982</t>
+          <t>445934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427032</t>
+          <t>489420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>454243</t>
+          <t>465265</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433196</t>
+          <t>446456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490205</t>
+          <t>483795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>861256</t>
+          <t>934623</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>828318</t>
+          <t>904714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>903180</t>
+          <t>964115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534990</t>
+          <t>617455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>589907</t>
+          <t>621032</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>589907</t>
+          <t>621032</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>589907</t>
+          <t>621032</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1124897</t>
+          <t>1238487</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1124897</t>
+          <t>1238487</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1124897</t>
+          <t>1238487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>63753</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>83245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74035</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>67557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87231</t>
+          <t>94856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>131245</t>
+          <t>144423</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>122072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164258</t>
+          <t>165342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>102270</t>
+          <t>112236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>93734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151475</t>
+          <t>134076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84906</t>
+          <t>96364</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68792</t>
+          <t>82385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99513</t>
+          <t>111490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187176</t>
+          <t>208600</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114946</t>
+          <t>183742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233830</t>
+          <t>232166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>728306</t>
+          <t>524629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>656192</t>
+          <t>499757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>821748</t>
+          <t>548063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>553094</t>
+          <t>558965</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534870</t>
+          <t>539821</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>579872</t>
+          <t>577311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1281400</t>
+          <t>1083595</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1209805</t>
+          <t>1052560</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1420631</t>
+          <t>1112044</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712035</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712035</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712035</t>
+          <t>735999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1599822</t>
+          <t>1436617</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1599822</t>
+          <t>1436617</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1599822</t>
+          <t>1436617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44006</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57102</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>94305</t>
+          <t>104971</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79271</t>
+          <t>87316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110873</t>
+          <t>121658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68147</t>
+          <t>75396</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>60262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83909</t>
+          <t>91957</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79034</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67555</t>
+          <t>76540</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93385</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>147181</t>
+          <t>164468</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128481</t>
+          <t>144994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167198</t>
+          <t>187000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>449082</t>
+          <t>487046</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>430546</t>
+          <t>468479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>465725</t>
+          <t>508741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>417960</t>
+          <t>461032</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>401829</t>
+          <t>442915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>432429</t>
+          <t>476493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>867041</t>
+          <t>948078</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>842519</t>
+          <t>923022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>889466</t>
+          <t>972949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547293</t>
+          <t>608170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1108526</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>238498</t>
+          <t>39898</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47800</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>451973</t>
+          <t>49940</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>269422</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>64107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>630830</t>
+          <t>88422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>46780</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>64422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>59555</t>
+          <t>65603</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>54426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>106335</t>
+          <t>116897</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140599</t>
+          <t>134040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -14883,69 +14883,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>290461</t>
+          <t>320260</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277241</t>
+          <t>305434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>302618</t>
+          <t>332926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>75,03%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>81,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>331813</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>318464</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>345006</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>72,82%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>78,89%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>75,3%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>308600</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>129713</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>472281</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>50,87%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>77,85%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1091</t>
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>599061</t>
+          <t>652073</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289678</t>
+          <t>632083</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>764707</t>
+          <t>670660</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>606653</t>
+          <t>437314</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>606653</t>
+          <t>437314</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>606653</t>
+          <t>437314</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>844394</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>844394</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>974818</t>
+          <t>844394</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>39727</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>62767</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>45481</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51041</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>71914</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52971</t>
+          <t>60766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>83975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>104337</t>
+          <t>117395</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91235</t>
+          <t>101065</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>121712</t>
+          <t>135157</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>245358</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>213754</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>234698</t>
+          <t>256304</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>333735</t>
+          <t>361035</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>320118</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>346163</t>
+          <t>374521</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>559709</t>
+          <t>606393</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>542241</t>
+          <t>587156</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>576378</t>
+          <t>624764</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282359</t>
+          <t>309775</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>464064</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>464064</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>464064</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707644</t>
+          <t>773839</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707644</t>
+          <t>773839</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707644</t>
+          <t>773839</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>266415</t>
+          <t>294534</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>260675</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>310529</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>512233</t>
+          <t>344599</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>313415</t>
+          <t>310309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1111643</t>
+          <t>376029</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>778647</t>
+          <t>639134</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>568924</t>
+          <t>588594</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1466265</t>
+          <t>687852</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>419503</t>
+          <t>468365</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>335004</t>
+          <t>424462</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>473837</t>
+          <t>519663</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>536242</t>
+          <t>537043</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>446845</t>
+          <t>500523</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>728721</t>
+          <t>579309</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>955746</t>
+          <t>1005407</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>843507</t>
+          <t>948171</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1158282</t>
+          <t>1067289</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2772151</t>
+          <t>2766058</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2695481</t>
+          <t>2708578</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2912984</t>
+          <t>2821458</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2657832</t>
+          <t>2848207</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2165341</t>
+          <t>2798896</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2848636</t>
+          <t>2892707</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5429983</t>
+          <t>5614265</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4899739</t>
+          <t>5536022</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5653815</t>
+          <t>5680289</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3458069</t>
+          <t>3528957</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3706307</t>
+          <t>3729849</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7164376</t>
+          <t>7258806</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
